--- a/datos/indicadores_adelantados/transporte/indice_general_transporte_2017_2026.xlsx
+++ b/datos/indicadores_adelantados/transporte/indice_general_transporte_2017_2026.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="W:\1. Página Web\2026 - 05. Mayo\Transporte 03-26\Año referencial 2017\Indicadores\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="W:\11. Otros\TRANS AGQ\Cuadros de salida Transporte\Pagina web\Indicadores\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3195C30D-ED6E-4433-B599-6CBFB6E83C61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19B9C095-64D6-409C-8ABB-E68DBD26641E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="743" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,14 +23,14 @@
     <sheet name="Ponderadores" sheetId="14" state="hidden" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">Indice!$B$2:$H$138</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Indice!$B$2:$H$140</definedName>
   </definedNames>
-  <calcPr calcId="191029" calcMode="manual"/>
+  <calcPr calcId="181029" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="799" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="802" uniqueCount="59">
   <si>
     <t>PERIODO</t>
   </si>
@@ -551,7 +551,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="77">
+  <cellXfs count="79">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -704,6 +704,12 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="2" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="4" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="4" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -20178,8 +20184,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B1:L142"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <dimension ref="B1:L148"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="1.7109375" style="1" customWidth="1"/>
     <col min="2" max="2" width="17.7109375" style="1" customWidth="1"/>
@@ -20189,15 +20195,15 @@
   <sheetData>
     <row r="1" spans="2:12" ht="69.95" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="2" spans="2:12" s="17" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B2" s="68" t="s">
+      <c r="B2" s="70" t="s">
         <v>54</v>
       </c>
-      <c r="C2" s="68"/>
-      <c r="D2" s="68"/>
-      <c r="E2" s="68"/>
-      <c r="F2" s="68"/>
-      <c r="G2" s="68"/>
-      <c r="H2" s="68"/>
+      <c r="C2" s="70"/>
+      <c r="D2" s="70"/>
+      <c r="E2" s="70"/>
+      <c r="F2" s="70"/>
+      <c r="G2" s="70"/>
+      <c r="H2" s="70"/>
     </row>
     <row r="3" spans="2:12" s="17" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B3" s="47" t="s">
@@ -20211,36 +20217,36 @@
       <c r="H3" s="47"/>
     </row>
     <row r="4" spans="2:12" s="17" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="70" t="s">
+      <c r="B4" s="72" t="s">
         <v>0</v>
       </c>
-      <c r="C4" s="69" t="s">
+      <c r="C4" s="71" t="s">
         <v>1</v>
       </c>
-      <c r="D4" s="69" t="s">
+      <c r="D4" s="71" t="s">
         <v>2</v>
       </c>
-      <c r="E4" s="69" t="s">
+      <c r="E4" s="71" t="s">
         <v>3</v>
       </c>
-      <c r="F4" s="69" t="s">
+      <c r="F4" s="71" t="s">
         <v>4</v>
       </c>
-      <c r="G4" s="69" t="s">
+      <c r="G4" s="71" t="s">
         <v>28</v>
       </c>
-      <c r="H4" s="69" t="s">
+      <c r="H4" s="71" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="5" spans="2:12" s="17" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B5" s="71"/>
-      <c r="C5" s="69"/>
-      <c r="D5" s="69"/>
-      <c r="E5" s="69"/>
-      <c r="F5" s="69"/>
-      <c r="G5" s="69"/>
-      <c r="H5" s="69" t="s">
+      <c r="B5" s="73"/>
+      <c r="C5" s="71"/>
+      <c r="D5" s="71"/>
+      <c r="E5" s="71"/>
+      <c r="F5" s="71"/>
+      <c r="G5" s="71"/>
+      <c r="H5" s="71" t="s">
         <v>6</v>
       </c>
     </row>
@@ -23162,22 +23168,22 @@
         <v>53</v>
       </c>
       <c r="C133" s="51">
-        <v>80.591506685948303</v>
+        <v>83.523793529459098</v>
       </c>
       <c r="D133" s="51">
-        <v>92.493278435463395</v>
+        <v>97.767732044752506</v>
       </c>
       <c r="E133" s="51">
-        <v>131.51683200521299</v>
+        <v>116.582317554854</v>
       </c>
       <c r="F133" s="51">
-        <v>90.107598581908107</v>
+        <v>88.548861224754404</v>
       </c>
       <c r="G133" s="51">
-        <v>86.917517468640995</v>
+        <v>88.0330219974161</v>
       </c>
       <c r="H133" s="51">
-        <v>93.671695529915993</v>
+        <v>94.735561351197603</v>
       </c>
     </row>
     <row r="134" spans="2:8" x14ac:dyDescent="0.2">
@@ -23194,13 +23200,13 @@
         <v>130.091500619057</v>
       </c>
       <c r="F134" s="49">
-        <v>93.271998410747699</v>
+        <v>93.520222046037503</v>
       </c>
       <c r="G134" s="53">
         <v>86.504367443735703</v>
       </c>
       <c r="H134" s="49">
-        <v>88.645508498548097</v>
+        <v>88.658242371038497</v>
       </c>
     </row>
     <row r="135" spans="2:8" x14ac:dyDescent="0.2">
@@ -23217,13 +23223,13 @@
         <v>109.56670480906401</v>
       </c>
       <c r="F135" s="49">
-        <v>82.204813719819896</v>
+        <v>82.257435317945905</v>
       </c>
       <c r="G135" s="53">
         <v>82.505571671196805</v>
       </c>
       <c r="H135" s="49">
-        <v>86.977551781855894</v>
+        <v>86.980251269839798</v>
       </c>
     </row>
     <row r="136" spans="2:8" x14ac:dyDescent="0.2">
@@ -23237,7 +23243,7 @@
         <v>109.967017272513</v>
       </c>
       <c r="E136" s="53">
-        <v>154.892290587519</v>
+        <v>114.15337810267199</v>
       </c>
       <c r="F136" s="49">
         <v>94.845983615156698</v>
@@ -23246,40 +23252,56 @@
         <v>91.742613290990505</v>
       </c>
       <c r="H136" s="49">
-        <v>105.392026309344</v>
+        <v>101.33529060167101</v>
       </c>
     </row>
     <row r="137" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B137" s="55" t="s">
+      <c r="B137" s="48" t="s">
+        <v>10</v>
+      </c>
+      <c r="C137" s="53">
+        <v>92.320654059991398</v>
+      </c>
+      <c r="D137" s="53">
+        <v>113.59109287262</v>
+      </c>
+      <c r="E137" s="53">
+        <v>112.51768668862201</v>
+      </c>
+      <c r="F137" s="49">
+        <v>83.571803919877397</v>
+      </c>
+      <c r="G137" s="53">
+        <v>91.379535583741401</v>
+      </c>
+      <c r="H137" s="49">
+        <v>101.968461162241</v>
+      </c>
+    </row>
+    <row r="138" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B138" s="48"/>
+      <c r="C138" s="53"/>
+      <c r="D138" s="53"/>
+      <c r="E138" s="53"/>
+      <c r="F138" s="49"/>
+      <c r="G138" s="53"/>
+      <c r="H138" s="49"/>
+    </row>
+    <row r="139" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B139" s="55" t="s">
         <v>52</v>
       </c>
-      <c r="C137" s="43"/>
-      <c r="D137" s="43"/>
-      <c r="E137" s="44"/>
-      <c r="F137" s="43"/>
-      <c r="G137" s="43"/>
-      <c r="H137" s="44"/>
-    </row>
-    <row r="138" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B138" s="56" t="s">
+      <c r="C139" s="43"/>
+      <c r="D139" s="43"/>
+      <c r="E139" s="44"/>
+      <c r="F139" s="43"/>
+      <c r="G139" s="43"/>
+      <c r="H139" s="44"/>
+    </row>
+    <row r="140" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B140" s="56" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="139" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="C139" s="65"/>
-      <c r="D139" s="65"/>
-      <c r="E139" s="65"/>
-      <c r="F139" s="65"/>
-      <c r="G139" s="65"/>
-      <c r="H139" s="65"/>
-    </row>
-    <row r="140" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="C140" s="65"/>
-      <c r="D140" s="65"/>
-      <c r="E140" s="65"/>
-      <c r="F140" s="65"/>
-      <c r="G140" s="65"/>
-      <c r="H140" s="65"/>
     </row>
     <row r="141" spans="2:8" x14ac:dyDescent="0.2">
       <c r="C141" s="65"/>
@@ -23296,6 +23318,54 @@
       <c r="F142" s="65"/>
       <c r="G142" s="65"/>
       <c r="H142" s="65"/>
+    </row>
+    <row r="143" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="C143" s="65"/>
+      <c r="D143" s="65"/>
+      <c r="E143" s="65"/>
+      <c r="F143" s="65"/>
+      <c r="G143" s="65"/>
+      <c r="H143" s="65"/>
+    </row>
+    <row r="144" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="C144" s="65"/>
+      <c r="D144" s="65"/>
+      <c r="E144" s="65"/>
+      <c r="F144" s="65"/>
+      <c r="G144" s="65"/>
+      <c r="H144" s="65"/>
+    </row>
+    <row r="145" spans="3:8" x14ac:dyDescent="0.2">
+      <c r="C145" s="68"/>
+      <c r="D145" s="68"/>
+      <c r="E145" s="68"/>
+      <c r="F145" s="68"/>
+      <c r="G145" s="68"/>
+      <c r="H145" s="68"/>
+    </row>
+    <row r="146" spans="3:8" x14ac:dyDescent="0.2">
+      <c r="C146" s="68"/>
+      <c r="D146" s="68"/>
+      <c r="E146" s="68"/>
+      <c r="F146" s="68"/>
+      <c r="G146" s="68"/>
+      <c r="H146" s="68"/>
+    </row>
+    <row r="147" spans="3:8" x14ac:dyDescent="0.2">
+      <c r="C147" s="68"/>
+      <c r="D147" s="68"/>
+      <c r="E147" s="68"/>
+      <c r="F147" s="68"/>
+      <c r="G147" s="68"/>
+      <c r="H147" s="68"/>
+    </row>
+    <row r="148" spans="3:8" x14ac:dyDescent="0.2">
+      <c r="C148" s="68"/>
+      <c r="D148" s="68"/>
+      <c r="E148" s="68"/>
+      <c r="F148" s="68"/>
+      <c r="G148" s="68"/>
+      <c r="H148" s="68"/>
     </row>
   </sheetData>
   <mergeCells count="8">
@@ -23319,8 +23389,8 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="B1:I129"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <dimension ref="B1:I136"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="1.7109375" style="13" customWidth="1"/>
     <col min="2" max="2" width="15.42578125" style="13" customWidth="1"/>
@@ -23332,15 +23402,15 @@
   <sheetData>
     <row r="1" spans="2:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="2" spans="2:9" s="17" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B2" s="72" t="s">
+      <c r="B2" s="74" t="s">
         <v>55</v>
       </c>
-      <c r="C2" s="72"/>
-      <c r="D2" s="72"/>
-      <c r="E2" s="72"/>
-      <c r="F2" s="72"/>
-      <c r="G2" s="72"/>
-      <c r="H2" s="72"/>
+      <c r="C2" s="74"/>
+      <c r="D2" s="74"/>
+      <c r="E2" s="74"/>
+      <c r="F2" s="74"/>
+      <c r="G2" s="74"/>
+      <c r="H2" s="74"/>
     </row>
     <row r="3" spans="2:9" s="17" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B3" s="33" t="s">
@@ -23354,37 +23424,37 @@
       <c r="H3" s="33"/>
     </row>
     <row r="4" spans="2:9" s="17" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="70" t="s">
+      <c r="B4" s="72" t="s">
         <v>0</v>
       </c>
-      <c r="C4" s="69" t="s">
+      <c r="C4" s="71" t="s">
         <v>1</v>
       </c>
-      <c r="D4" s="69" t="s">
+      <c r="D4" s="71" t="s">
         <v>2</v>
       </c>
-      <c r="E4" s="69" t="s">
+      <c r="E4" s="71" t="s">
         <v>3</v>
       </c>
-      <c r="F4" s="69" t="s">
+      <c r="F4" s="71" t="s">
         <v>4</v>
       </c>
-      <c r="G4" s="69" t="s">
+      <c r="G4" s="71" t="s">
         <v>28</v>
       </c>
-      <c r="H4" s="69" t="s">
+      <c r="H4" s="71" t="s">
         <v>5</v>
       </c>
       <c r="I4" s="58"/>
     </row>
     <row r="5" spans="2:9" s="17" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B5" s="71"/>
-      <c r="C5" s="69"/>
-      <c r="D5" s="69"/>
-      <c r="E5" s="69"/>
-      <c r="F5" s="69"/>
-      <c r="G5" s="69"/>
-      <c r="H5" s="69" t="s">
+      <c r="B5" s="73"/>
+      <c r="C5" s="71"/>
+      <c r="D5" s="71"/>
+      <c r="E5" s="71"/>
+      <c r="F5" s="71"/>
+      <c r="G5" s="71"/>
+      <c r="H5" s="71" t="s">
         <v>6</v>
       </c>
       <c r="I5" s="58"/>
@@ -26076,22 +26146,22 @@
         <v>53</v>
       </c>
       <c r="C119" s="51">
-        <v>25.494105701435299</v>
+        <v>17.7329054073622</v>
       </c>
       <c r="D119" s="51">
-        <v>-12.9911346134884</v>
+        <v>1.7391900011492401</v>
       </c>
       <c r="E119" s="51">
-        <v>-0.55580135244572704</v>
+        <v>-10.392174519202801</v>
       </c>
       <c r="F119" s="51">
-        <v>5.52027091268444</v>
+        <v>3.0741749446289601</v>
       </c>
       <c r="G119" s="51">
-        <v>7.1284603175471197</v>
+        <v>7.2453995663194197</v>
       </c>
       <c r="H119" s="51">
-        <v>-2.7178502219098299</v>
+        <v>2.39161402946739</v>
       </c>
       <c r="I119" s="61"/>
     </row>
@@ -26109,13 +26179,13 @@
         <v>-17.218301657618401</v>
       </c>
       <c r="F120" s="49">
-        <v>3.0947716119685502</v>
+        <v>3.36913647414509</v>
       </c>
       <c r="G120" s="49">
         <v>-1.66228355389559</v>
       </c>
       <c r="H120" s="49">
-        <v>-16.189114873029901</v>
+        <v>-16.177075491197801</v>
       </c>
       <c r="I120" s="61"/>
     </row>
@@ -26133,13 +26203,13 @@
         <v>-7.7433764969202903</v>
       </c>
       <c r="F121" s="49">
-        <v>3.9084750822270702</v>
+        <v>3.97498980040768</v>
       </c>
       <c r="G121" s="49">
         <v>6.8624496891670903</v>
       </c>
       <c r="H121" s="49">
-        <v>-7.9030519413401397</v>
+        <v>-7.9001935646723203</v>
       </c>
       <c r="I121" s="61"/>
     </row>
@@ -26154,7 +26224,7 @@
         <v>17.912006749217699</v>
       </c>
       <c r="E122" s="49">
-        <v>28.176865525108401</v>
+        <v>-5.5355038084635702</v>
       </c>
       <c r="F122" s="49">
         <v>9.5268428874073301</v>
@@ -26163,47 +26233,65 @@
         <v>17.276122404854899</v>
       </c>
       <c r="H122" s="49">
-        <v>18.877159840608599</v>
+        <v>14.301356186007199</v>
       </c>
       <c r="I122" s="61"/>
     </row>
-    <row r="123" spans="2:9" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="B123" s="63" t="s">
+    <row r="123" spans="2:9" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B123" s="48" t="s">
+        <v>10</v>
+      </c>
+      <c r="C123" s="49">
+        <v>1.3223761849026801</v>
+      </c>
+      <c r="D123" s="49">
+        <v>73.485380189412396</v>
+      </c>
+      <c r="E123" s="49">
+        <v>-9.0072444886629199</v>
+      </c>
+      <c r="F123" s="49">
+        <v>-4.4355154342652803</v>
+      </c>
+      <c r="G123" s="49">
+        <v>7.5804950670356703</v>
+      </c>
+      <c r="H123" s="49">
+        <v>25.5381755991856</v>
+      </c>
+      <c r="I123" s="61"/>
+    </row>
+    <row r="124" spans="2:9" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B124" s="48"/>
+      <c r="C124" s="49"/>
+      <c r="D124" s="49"/>
+      <c r="E124" s="49"/>
+      <c r="F124" s="49"/>
+      <c r="G124" s="49"/>
+      <c r="H124" s="49"/>
+      <c r="I124" s="61"/>
+    </row>
+    <row r="125" spans="2:9" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="B125" s="63" t="s">
         <v>52</v>
       </c>
-      <c r="C123" s="45"/>
-      <c r="D123" s="45"/>
-      <c r="E123" s="45"/>
-      <c r="F123" s="45"/>
-      <c r="G123" s="45"/>
-      <c r="H123" s="45"/>
-    </row>
-    <row r="124" spans="2:9" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="B124" s="64" t="s">
+      <c r="C125" s="45"/>
+      <c r="D125" s="45"/>
+      <c r="E125" s="45"/>
+      <c r="F125" s="45"/>
+      <c r="G125" s="45"/>
+      <c r="H125" s="45"/>
+    </row>
+    <row r="126" spans="2:9" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="B126" s="64" t="s">
         <v>21</v>
       </c>
-      <c r="C124" s="34"/>
-      <c r="D124" s="34"/>
-      <c r="E124" s="34"/>
-      <c r="F124" s="34"/>
-      <c r="G124" s="34"/>
-      <c r="H124" s="34"/>
-    </row>
-    <row r="126" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="C126" s="66"/>
-      <c r="D126" s="66"/>
-      <c r="E126" s="66"/>
-      <c r="F126" s="66"/>
-      <c r="G126" s="66"/>
-      <c r="H126" s="67"/>
-    </row>
-    <row r="127" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="C127" s="66"/>
-      <c r="D127" s="66"/>
-      <c r="E127" s="66"/>
-      <c r="F127" s="66"/>
-      <c r="G127" s="66"/>
-      <c r="H127" s="67"/>
+      <c r="C126" s="34"/>
+      <c r="D126" s="34"/>
+      <c r="E126" s="34"/>
+      <c r="F126" s="34"/>
+      <c r="G126" s="34"/>
+      <c r="H126" s="34"/>
     </row>
     <row r="128" spans="2:9" x14ac:dyDescent="0.2">
       <c r="C128" s="66"/>
@@ -26220,6 +26308,54 @@
       <c r="F129" s="66"/>
       <c r="G129" s="66"/>
       <c r="H129" s="67"/>
+    </row>
+    <row r="130" spans="3:8" x14ac:dyDescent="0.2">
+      <c r="C130" s="66"/>
+      <c r="D130" s="66"/>
+      <c r="E130" s="66"/>
+      <c r="F130" s="66"/>
+      <c r="G130" s="66"/>
+      <c r="H130" s="67"/>
+    </row>
+    <row r="131" spans="3:8" x14ac:dyDescent="0.2">
+      <c r="C131" s="66"/>
+      <c r="D131" s="66"/>
+      <c r="E131" s="66"/>
+      <c r="F131" s="66"/>
+      <c r="G131" s="66"/>
+      <c r="H131" s="67"/>
+    </row>
+    <row r="133" spans="3:8" x14ac:dyDescent="0.2">
+      <c r="C133" s="69"/>
+      <c r="D133" s="69"/>
+      <c r="E133" s="69"/>
+      <c r="F133" s="69"/>
+      <c r="G133" s="69"/>
+      <c r="H133" s="69"/>
+    </row>
+    <row r="134" spans="3:8" x14ac:dyDescent="0.2">
+      <c r="C134" s="69"/>
+      <c r="D134" s="69"/>
+      <c r="E134" s="69"/>
+      <c r="F134" s="69"/>
+      <c r="G134" s="69"/>
+      <c r="H134" s="69"/>
+    </row>
+    <row r="135" spans="3:8" x14ac:dyDescent="0.2">
+      <c r="C135" s="69"/>
+      <c r="D135" s="69"/>
+      <c r="E135" s="69"/>
+      <c r="F135" s="69"/>
+      <c r="G135" s="69"/>
+      <c r="H135" s="69"/>
+    </row>
+    <row r="136" spans="3:8" x14ac:dyDescent="0.2">
+      <c r="C136" s="69"/>
+      <c r="D136" s="69"/>
+      <c r="E136" s="69"/>
+      <c r="F136" s="69"/>
+      <c r="G136" s="69"/>
+      <c r="H136" s="69"/>
     </row>
   </sheetData>
   <mergeCells count="8">
@@ -26243,8 +26379,8 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="B1:I129"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <dimension ref="B1:I134"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="1.7109375" style="13" customWidth="1"/>
     <col min="2" max="2" width="15.42578125" style="13" customWidth="1"/>
@@ -26256,15 +26392,15 @@
   <sheetData>
     <row r="1" spans="2:9" ht="69.95" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="2" spans="2:9" s="17" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B2" s="72" t="s">
+      <c r="B2" s="74" t="s">
         <v>56</v>
       </c>
-      <c r="C2" s="72"/>
-      <c r="D2" s="72"/>
-      <c r="E2" s="72"/>
-      <c r="F2" s="72"/>
-      <c r="G2" s="72"/>
-      <c r="H2" s="72"/>
+      <c r="C2" s="74"/>
+      <c r="D2" s="74"/>
+      <c r="E2" s="74"/>
+      <c r="F2" s="74"/>
+      <c r="G2" s="74"/>
+      <c r="H2" s="74"/>
     </row>
     <row r="3" spans="2:9" s="17" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B3" s="33" t="s">
@@ -26278,37 +26414,37 @@
       <c r="H3" s="33"/>
     </row>
     <row r="4" spans="2:9" s="17" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="70" t="s">
+      <c r="B4" s="72" t="s">
         <v>0</v>
       </c>
-      <c r="C4" s="69" t="s">
+      <c r="C4" s="71" t="s">
         <v>1</v>
       </c>
-      <c r="D4" s="69" t="s">
+      <c r="D4" s="71" t="s">
         <v>2</v>
       </c>
-      <c r="E4" s="69" t="s">
+      <c r="E4" s="71" t="s">
         <v>3</v>
       </c>
-      <c r="F4" s="69" t="s">
+      <c r="F4" s="71" t="s">
         <v>4</v>
       </c>
-      <c r="G4" s="69" t="s">
+      <c r="G4" s="71" t="s">
         <v>28</v>
       </c>
-      <c r="H4" s="69" t="s">
+      <c r="H4" s="71" t="s">
         <v>5</v>
       </c>
       <c r="I4" s="58"/>
     </row>
     <row r="5" spans="2:9" s="17" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B5" s="71"/>
-      <c r="C5" s="69"/>
-      <c r="D5" s="69"/>
-      <c r="E5" s="69"/>
-      <c r="F5" s="69"/>
-      <c r="G5" s="69"/>
-      <c r="H5" s="69" t="s">
+      <c r="B5" s="73"/>
+      <c r="C5" s="71"/>
+      <c r="D5" s="71"/>
+      <c r="E5" s="71"/>
+      <c r="F5" s="71"/>
+      <c r="G5" s="71"/>
+      <c r="H5" s="71" t="s">
         <v>6</v>
       </c>
       <c r="I5" s="58"/>
@@ -29000,22 +29136,22 @@
         <v>53</v>
       </c>
       <c r="C119" s="51">
-        <v>25.494105701435299</v>
+        <v>17.7329054073622</v>
       </c>
       <c r="D119" s="51">
-        <v>-12.9911346134884</v>
+        <v>1.7391900011492401</v>
       </c>
       <c r="E119" s="51">
-        <v>-0.55580135244572704</v>
+        <v>-10.392174519202801</v>
       </c>
       <c r="F119" s="51">
-        <v>5.52027091268444</v>
+        <v>3.0741749446289601</v>
       </c>
       <c r="G119" s="51">
-        <v>7.1284603175471197</v>
+        <v>7.2453995663194197</v>
       </c>
       <c r="H119" s="51">
-        <v>-2.7178502219098299</v>
+        <v>2.39161402946739</v>
       </c>
       <c r="I119" s="61"/>
     </row>
@@ -29033,13 +29169,13 @@
         <v>-6.8950031646190402</v>
       </c>
       <c r="F120" s="49">
-        <v>2.71027205218184</v>
+        <v>2.9836136503550001</v>
       </c>
       <c r="G120" s="49">
         <v>-4.2755347999008499</v>
       </c>
       <c r="H120" s="49">
-        <v>-6.6332265838071001</v>
+        <v>-6.6198145045302299</v>
       </c>
       <c r="I120" s="61"/>
     </row>
@@ -29057,13 +29193,13 @@
         <v>-15.777199672786599</v>
       </c>
       <c r="F121" s="49">
-        <v>-11.865495410734701</v>
+        <v>-12.0431565298757</v>
       </c>
       <c r="G121" s="49">
         <v>-4.6226518853395504</v>
       </c>
       <c r="H121" s="49">
-        <v>-1.88160319111884</v>
+        <v>-1.8926509891502701</v>
       </c>
       <c r="I121" s="61"/>
     </row>
@@ -29078,56 +29214,74 @@
         <v>25.8754275033223</v>
       </c>
       <c r="E122" s="49">
-        <v>41.3680285972289</v>
+        <v>4.1861926044056199</v>
       </c>
       <c r="F122" s="49">
-        <v>15.377651652398299</v>
+        <v>15.3038424411761</v>
       </c>
       <c r="G122" s="49">
         <v>11.1956579812638</v>
       </c>
       <c r="H122" s="49">
-        <v>21.171525468631899</v>
+        <v>16.503791518487802</v>
       </c>
       <c r="I122" s="61"/>
     </row>
-    <row r="123" spans="2:9" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="B123" s="63" t="s">
+    <row r="123" spans="2:9" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B123" s="48" t="s">
+        <v>10</v>
+      </c>
+      <c r="C123" s="49">
+        <v>8.1185713630093499</v>
+      </c>
+      <c r="D123" s="49">
+        <v>3.2956023451341299</v>
+      </c>
+      <c r="E123" s="49">
+        <v>-1.4328891892965301</v>
+      </c>
+      <c r="F123" s="49">
+        <v>-11.8868287992299</v>
+      </c>
+      <c r="G123" s="49">
+        <v>-0.39575688355148497</v>
+      </c>
+      <c r="H123" s="49">
+        <v>0.62482730035171097</v>
+      </c>
+      <c r="I123" s="61"/>
+    </row>
+    <row r="124" spans="2:9" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B124" s="48"/>
+      <c r="C124" s="49"/>
+      <c r="D124" s="49"/>
+      <c r="E124" s="49"/>
+      <c r="F124" s="49"/>
+      <c r="G124" s="49"/>
+      <c r="H124" s="49"/>
+      <c r="I124" s="61"/>
+    </row>
+    <row r="125" spans="2:9" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="B125" s="63" t="s">
         <v>52</v>
       </c>
-      <c r="C123" s="45"/>
-      <c r="D123" s="45"/>
-      <c r="E123" s="45"/>
-      <c r="F123" s="45"/>
-      <c r="G123" s="45"/>
-      <c r="H123" s="45"/>
-    </row>
-    <row r="124" spans="2:9" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="B124" s="64" t="s">
+      <c r="C125" s="45"/>
+      <c r="D125" s="45"/>
+      <c r="E125" s="45"/>
+      <c r="F125" s="45"/>
+      <c r="G125" s="45"/>
+      <c r="H125" s="45"/>
+    </row>
+    <row r="126" spans="2:9" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="B126" s="64" t="s">
         <v>21</v>
       </c>
-      <c r="C124" s="34"/>
-      <c r="D124" s="34"/>
-      <c r="E124" s="34"/>
-      <c r="F124" s="34"/>
-      <c r="G124" s="34"/>
-      <c r="H124" s="34"/>
-    </row>
-    <row r="126" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="C126" s="66"/>
-      <c r="D126" s="66"/>
-      <c r="E126" s="66"/>
-      <c r="F126" s="66"/>
-      <c r="G126" s="66"/>
-      <c r="H126" s="67"/>
-    </row>
-    <row r="127" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="C127" s="66"/>
-      <c r="D127" s="66"/>
-      <c r="E127" s="66"/>
-      <c r="F127" s="66"/>
-      <c r="G127" s="66"/>
-      <c r="H127" s="67"/>
+      <c r="C126" s="34"/>
+      <c r="D126" s="34"/>
+      <c r="E126" s="34"/>
+      <c r="F126" s="34"/>
+      <c r="G126" s="34"/>
+      <c r="H126" s="34"/>
     </row>
     <row r="128" spans="2:9" x14ac:dyDescent="0.2">
       <c r="C128" s="66"/>
@@ -29144,6 +29298,46 @@
       <c r="F129" s="66"/>
       <c r="G129" s="66"/>
       <c r="H129" s="67"/>
+    </row>
+    <row r="130" spans="3:8" x14ac:dyDescent="0.2">
+      <c r="C130" s="66"/>
+      <c r="D130" s="66"/>
+      <c r="E130" s="66"/>
+      <c r="F130" s="66"/>
+      <c r="G130" s="66"/>
+      <c r="H130" s="67"/>
+    </row>
+    <row r="131" spans="3:8" x14ac:dyDescent="0.2">
+      <c r="C131" s="66"/>
+      <c r="D131" s="66"/>
+      <c r="E131" s="66"/>
+      <c r="F131" s="66"/>
+      <c r="G131" s="66"/>
+      <c r="H131" s="66"/>
+    </row>
+    <row r="132" spans="3:8" x14ac:dyDescent="0.2">
+      <c r="C132" s="66"/>
+      <c r="D132" s="66"/>
+      <c r="E132" s="66"/>
+      <c r="F132" s="66"/>
+      <c r="G132" s="66"/>
+      <c r="H132" s="66"/>
+    </row>
+    <row r="133" spans="3:8" x14ac:dyDescent="0.2">
+      <c r="C133" s="66"/>
+      <c r="D133" s="66"/>
+      <c r="E133" s="66"/>
+      <c r="F133" s="66"/>
+      <c r="G133" s="66"/>
+      <c r="H133" s="66"/>
+    </row>
+    <row r="134" spans="3:8" x14ac:dyDescent="0.2">
+      <c r="C134" s="66"/>
+      <c r="D134" s="66"/>
+      <c r="E134" s="66"/>
+      <c r="F134" s="66"/>
+      <c r="G134" s="66"/>
+      <c r="H134" s="66"/>
     </row>
   </sheetData>
   <mergeCells count="8">
@@ -29167,7 +29361,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:I78"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="11.42578125" style="1"/>
     <col min="2" max="2" width="17.7109375" style="1" customWidth="1"/>
@@ -29176,15 +29370,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" s="17" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B1" s="73" t="s">
+      <c r="B1" s="75" t="s">
         <v>29</v>
       </c>
-      <c r="C1" s="74"/>
-      <c r="D1" s="74"/>
-      <c r="E1" s="74"/>
-      <c r="F1" s="74"/>
-      <c r="G1" s="74"/>
-      <c r="H1" s="74"/>
+      <c r="C1" s="76"/>
+      <c r="D1" s="76"/>
+      <c r="E1" s="76"/>
+      <c r="F1" s="76"/>
+      <c r="G1" s="76"/>
+      <c r="H1" s="76"/>
     </row>
     <row r="2" spans="1:9" s="17" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B2" s="18" t="s">
@@ -29198,22 +29392,22 @@
       <c r="H2" s="20"/>
     </row>
     <row r="3" spans="1:9" s="17" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B3" s="75" t="s">
+      <c r="B3" s="77" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="75" t="s">
+      <c r="C3" s="77" t="s">
         <v>1</v>
       </c>
-      <c r="D3" s="75" t="s">
+      <c r="D3" s="77" t="s">
         <v>2</v>
       </c>
-      <c r="E3" s="75" t="s">
+      <c r="E3" s="77" t="s">
         <v>3</v>
       </c>
-      <c r="F3" s="75" t="s">
+      <c r="F3" s="77" t="s">
         <v>4</v>
       </c>
-      <c r="G3" s="75" t="s">
+      <c r="G3" s="77" t="s">
         <v>28</v>
       </c>
       <c r="H3" s="21" t="s">
@@ -29221,12 +29415,12 @@
       </c>
     </row>
     <row r="4" spans="1:9" s="17" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="76"/>
-      <c r="C4" s="76"/>
-      <c r="D4" s="76"/>
-      <c r="E4" s="76"/>
-      <c r="F4" s="76"/>
-      <c r="G4" s="76"/>
+      <c r="B4" s="78"/>
+      <c r="C4" s="78"/>
+      <c r="D4" s="78"/>
+      <c r="E4" s="78"/>
+      <c r="F4" s="78"/>
+      <c r="G4" s="78"/>
       <c r="H4" s="22" t="s">
         <v>6</v>
       </c>
@@ -30984,7 +31178,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:D79"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="11.42578125" style="13"/>
     <col min="2" max="2" width="15.42578125" style="13" customWidth="1"/>
@@ -31003,20 +31197,20 @@
       </c>
     </row>
     <row r="3" spans="1:4" s="23" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B3" s="75" t="s">
+      <c r="B3" s="77" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="75" t="s">
+      <c r="C3" s="77" t="s">
         <v>44</v>
       </c>
-      <c r="D3" s="75" t="s">
+      <c r="D3" s="77" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="4" spans="1:4" s="23" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="76"/>
-      <c r="C4" s="76"/>
-      <c r="D4" s="76"/>
+      <c r="B4" s="78"/>
+      <c r="C4" s="78"/>
+      <c r="D4" s="78"/>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.2">
       <c r="B5" s="14"/>
@@ -31870,7 +32064,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:G81"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="11.42578125" style="1"/>
     <col min="2" max="2" width="17.7109375" style="1" customWidth="1"/>
@@ -31879,14 +32073,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" s="17" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B1" s="73" t="s">
+      <c r="B1" s="75" t="s">
         <v>23</v>
       </c>
-      <c r="C1" s="74"/>
-      <c r="D1" s="74"/>
-      <c r="E1" s="74"/>
-      <c r="F1" s="74"/>
-      <c r="G1" s="74"/>
+      <c r="C1" s="76"/>
+      <c r="D1" s="76"/>
+      <c r="E1" s="76"/>
+      <c r="F1" s="76"/>
+      <c r="G1" s="76"/>
     </row>
     <row r="2" spans="1:7" s="17" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B2" s="18" t="s">
@@ -31899,32 +32093,32 @@
       <c r="G2" s="20"/>
     </row>
     <row r="3" spans="1:7" s="17" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B3" s="75" t="s">
+      <c r="B3" s="77" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="75" t="s">
+      <c r="C3" s="77" t="s">
         <v>1</v>
       </c>
-      <c r="D3" s="75" t="s">
+      <c r="D3" s="77" t="s">
         <v>2</v>
       </c>
-      <c r="E3" s="75" t="s">
+      <c r="E3" s="77" t="s">
         <v>3</v>
       </c>
-      <c r="F3" s="75" t="s">
+      <c r="F3" s="77" t="s">
         <v>4</v>
       </c>
-      <c r="G3" s="75" t="s">
+      <c r="G3" s="77" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="4" spans="1:7" s="17" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="76"/>
-      <c r="C4" s="76"/>
-      <c r="D4" s="76"/>
-      <c r="E4" s="76"/>
-      <c r="F4" s="76"/>
-      <c r="G4" s="76"/>
+      <c r="B4" s="78"/>
+      <c r="C4" s="78"/>
+      <c r="D4" s="78"/>
+      <c r="E4" s="78"/>
+      <c r="F4" s="78"/>
+      <c r="G4" s="78"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B5" s="2"/>
@@ -33482,7 +33676,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:O1048576"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="16384" width="11.42578125" style="13"/>
   </cols>
@@ -33500,38 +33694,38 @@
       </c>
     </row>
     <row r="28" spans="1:15" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B28" s="69" t="s">
+      <c r="B28" s="71" t="s">
         <v>1</v>
       </c>
-      <c r="C28" s="69" t="s">
+      <c r="C28" s="71" t="s">
         <v>2</v>
       </c>
-      <c r="D28" s="69" t="s">
+      <c r="D28" s="71" t="s">
         <v>3</v>
       </c>
-      <c r="E28" s="69" t="s">
+      <c r="E28" s="71" t="s">
         <v>4</v>
       </c>
-      <c r="F28" s="69" t="s">
+      <c r="F28" s="71" t="s">
         <v>28</v>
       </c>
-      <c r="G28" s="69" t="s">
+      <c r="G28" s="71" t="s">
         <v>46</v>
       </c>
-      <c r="H28" s="69" t="s">
+      <c r="H28" s="71" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="29" spans="1:15" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B29" s="69"/>
-      <c r="C29" s="69"/>
-      <c r="D29" s="69"/>
-      <c r="E29" s="69"/>
-      <c r="F29" s="69"/>
-      <c r="G29" s="69" t="s">
+      <c r="B29" s="71"/>
+      <c r="C29" s="71"/>
+      <c r="D29" s="71"/>
+      <c r="E29" s="71"/>
+      <c r="F29" s="71"/>
+      <c r="G29" s="71" t="s">
         <v>6</v>
       </c>
-      <c r="H29" s="69" t="s">
+      <c r="H29" s="71" t="s">
         <v>47</v>
       </c>
       <c r="N29" s="38" t="s">

--- a/datos/indicadores_adelantados/transporte/indice_general_transporte_2017_2026.xlsx
+++ b/datos/indicadores_adelantados/transporte/indice_general_transporte_2017_2026.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="W:\11. Otros\TRANS AGQ\Cuadros de salida Transporte\Pagina web\Indicadores\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\clopez\Documents\Transporte\TRANS AGQ\Cuadros de salida Transporte\Pagina web\Indicadores\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19B9C095-64D6-409C-8ABB-E68DBD26641E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0037C23E-747C-45FB-B2BA-55D8D7D7DCFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="743" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,14 +23,14 @@
     <sheet name="Ponderadores" sheetId="14" state="hidden" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">Indice!$B$2:$H$140</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Indice!$B$2:$H$141</definedName>
   </definedNames>
   <calcPr calcId="181029" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="802" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="805" uniqueCount="59">
   <si>
     <t>PERIODO</t>
   </si>
@@ -20184,7 +20184,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B1:L148"/>
+  <dimension ref="B1:L149"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="1.7109375" style="1" customWidth="1"/>
@@ -23168,22 +23168,22 @@
         <v>53</v>
       </c>
       <c r="C133" s="51">
-        <v>83.523793529459098</v>
+        <v>85.647565273994701</v>
       </c>
       <c r="D133" s="51">
-        <v>97.767732044752506</v>
+        <v>88.998634781700005</v>
       </c>
       <c r="E133" s="51">
-        <v>116.582317554854</v>
+        <v>117.410077812916</v>
       </c>
       <c r="F133" s="51">
-        <v>88.548861224754404</v>
+        <v>89.5088107948106</v>
       </c>
       <c r="G133" s="51">
-        <v>88.0330219974161</v>
+        <v>85.327925407727605</v>
       </c>
       <c r="H133" s="51">
-        <v>94.735561351197603</v>
+        <v>90.207404815957005</v>
       </c>
     </row>
     <row r="134" spans="2:8" x14ac:dyDescent="0.2">
@@ -23279,37 +23279,52 @@
       </c>
     </row>
     <row r="138" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B138" s="48"/>
-      <c r="C138" s="53"/>
-      <c r="D138" s="53"/>
-      <c r="E138" s="53"/>
-      <c r="F138" s="49"/>
-      <c r="G138" s="53"/>
-      <c r="H138" s="49"/>
+      <c r="B138" s="48" t="s">
+        <v>11</v>
+      </c>
+      <c r="C138" s="53">
+        <v>94.142652252137097</v>
+      </c>
+      <c r="D138" s="53">
+        <v>53.922245729489802</v>
+      </c>
+      <c r="E138" s="53">
+        <v>120.721118845166</v>
+      </c>
+      <c r="F138" s="49">
+        <v>93.348609075035498</v>
+      </c>
+      <c r="G138" s="53">
+        <v>74.507539048973797</v>
+      </c>
+      <c r="H138" s="49">
+        <v>72.094778674994501</v>
+      </c>
     </row>
     <row r="139" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B139" s="55" t="s">
+      <c r="B139" s="48"/>
+      <c r="C139" s="53"/>
+      <c r="D139" s="53"/>
+      <c r="E139" s="53"/>
+      <c r="F139" s="49"/>
+      <c r="G139" s="53"/>
+      <c r="H139" s="49"/>
+    </row>
+    <row r="140" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B140" s="55" t="s">
         <v>52</v>
       </c>
-      <c r="C139" s="43"/>
-      <c r="D139" s="43"/>
-      <c r="E139" s="44"/>
-      <c r="F139" s="43"/>
-      <c r="G139" s="43"/>
-      <c r="H139" s="44"/>
-    </row>
-    <row r="140" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B140" s="56" t="s">
+      <c r="C140" s="43"/>
+      <c r="D140" s="43"/>
+      <c r="E140" s="44"/>
+      <c r="F140" s="43"/>
+      <c r="G140" s="43"/>
+      <c r="H140" s="44"/>
+    </row>
+    <row r="141" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B141" s="56" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="141" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="C141" s="65"/>
-      <c r="D141" s="65"/>
-      <c r="E141" s="65"/>
-      <c r="F141" s="65"/>
-      <c r="G141" s="65"/>
-      <c r="H141" s="65"/>
     </row>
     <row r="142" spans="2:8" x14ac:dyDescent="0.2">
       <c r="C142" s="65"/>
@@ -23336,12 +23351,12 @@
       <c r="H144" s="65"/>
     </row>
     <row r="145" spans="3:8" x14ac:dyDescent="0.2">
-      <c r="C145" s="68"/>
-      <c r="D145" s="68"/>
-      <c r="E145" s="68"/>
-      <c r="F145" s="68"/>
-      <c r="G145" s="68"/>
-      <c r="H145" s="68"/>
+      <c r="C145" s="65"/>
+      <c r="D145" s="65"/>
+      <c r="E145" s="65"/>
+      <c r="F145" s="65"/>
+      <c r="G145" s="65"/>
+      <c r="H145" s="65"/>
     </row>
     <row r="146" spans="3:8" x14ac:dyDescent="0.2">
       <c r="C146" s="68"/>
@@ -23366,6 +23381,14 @@
       <c r="F148" s="68"/>
       <c r="G148" s="68"/>
       <c r="H148" s="68"/>
+    </row>
+    <row r="149" spans="3:8" x14ac:dyDescent="0.2">
+      <c r="C149" s="68"/>
+      <c r="D149" s="68"/>
+      <c r="E149" s="68"/>
+      <c r="F149" s="68"/>
+      <c r="G149" s="68"/>
+      <c r="H149" s="68"/>
     </row>
   </sheetData>
   <mergeCells count="8">
@@ -23389,7 +23412,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="B1:I136"/>
+  <dimension ref="B1:I137"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="1.7109375" style="13" customWidth="1"/>
@@ -26146,22 +26169,22 @@
         <v>53</v>
       </c>
       <c r="C119" s="51">
-        <v>17.7329054073622</v>
+        <v>8.5143876907174096</v>
       </c>
       <c r="D119" s="51">
-        <v>1.7391900011492401</v>
+        <v>-2.6864561891104399</v>
       </c>
       <c r="E119" s="51">
-        <v>-10.392174519202801</v>
+        <v>-9.8337381063185596</v>
       </c>
       <c r="F119" s="51">
-        <v>3.0741749446289601</v>
+        <v>2.5808355999792099</v>
       </c>
       <c r="G119" s="51">
-        <v>7.2453995663194197</v>
+        <v>4.2411815470479599</v>
       </c>
       <c r="H119" s="51">
-        <v>2.39161402946739</v>
+        <v>-0.59503429813638298</v>
       </c>
       <c r="I119" s="61"/>
     </row>
@@ -26262,44 +26285,60 @@
       <c r="I123" s="61"/>
     </row>
     <row r="124" spans="2:9" s="1" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B124" s="48"/>
-      <c r="C124" s="49"/>
-      <c r="D124" s="49"/>
-      <c r="E124" s="49"/>
-      <c r="F124" s="49"/>
-      <c r="G124" s="49"/>
-      <c r="H124" s="49"/>
+      <c r="B124" s="48" t="s">
+        <v>11</v>
+      </c>
+      <c r="C124" s="49">
+        <v>-15.082052726437899</v>
+      </c>
+      <c r="D124" s="49">
+        <v>-26.024476915061999</v>
+      </c>
+      <c r="E124" s="49">
+        <v>-7.6095878743040499</v>
+      </c>
+      <c r="F124" s="49">
+        <v>0.75113118193657202</v>
+      </c>
+      <c r="G124" s="49">
+        <v>-7.9459390819057596</v>
+      </c>
+      <c r="H124" s="49">
+        <v>-13.809465770313199</v>
+      </c>
       <c r="I124" s="61"/>
     </row>
-    <row r="125" spans="2:9" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="B125" s="63" t="s">
+    <row r="125" spans="2:9" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B125" s="48"/>
+      <c r="C125" s="49"/>
+      <c r="D125" s="49"/>
+      <c r="E125" s="49"/>
+      <c r="F125" s="49"/>
+      <c r="G125" s="49"/>
+      <c r="H125" s="49"/>
+      <c r="I125" s="61"/>
+    </row>
+    <row r="126" spans="2:9" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="B126" s="63" t="s">
         <v>52</v>
       </c>
-      <c r="C125" s="45"/>
-      <c r="D125" s="45"/>
-      <c r="E125" s="45"/>
-      <c r="F125" s="45"/>
-      <c r="G125" s="45"/>
-      <c r="H125" s="45"/>
-    </row>
-    <row r="126" spans="2:9" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="B126" s="64" t="s">
+      <c r="C126" s="45"/>
+      <c r="D126" s="45"/>
+      <c r="E126" s="45"/>
+      <c r="F126" s="45"/>
+      <c r="G126" s="45"/>
+      <c r="H126" s="45"/>
+    </row>
+    <row r="127" spans="2:9" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="B127" s="64" t="s">
         <v>21</v>
       </c>
-      <c r="C126" s="34"/>
-      <c r="D126" s="34"/>
-      <c r="E126" s="34"/>
-      <c r="F126" s="34"/>
-      <c r="G126" s="34"/>
-      <c r="H126" s="34"/>
-    </row>
-    <row r="128" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="C128" s="66"/>
-      <c r="D128" s="66"/>
-      <c r="E128" s="66"/>
-      <c r="F128" s="66"/>
-      <c r="G128" s="66"/>
-      <c r="H128" s="67"/>
+      <c r="C127" s="34"/>
+      <c r="D127" s="34"/>
+      <c r="E127" s="34"/>
+      <c r="F127" s="34"/>
+      <c r="G127" s="34"/>
+      <c r="H127" s="34"/>
     </row>
     <row r="129" spans="3:8" x14ac:dyDescent="0.2">
       <c r="C129" s="66"/>
@@ -26325,13 +26364,13 @@
       <c r="G131" s="66"/>
       <c r="H131" s="67"/>
     </row>
-    <row r="133" spans="3:8" x14ac:dyDescent="0.2">
-      <c r="C133" s="69"/>
-      <c r="D133" s="69"/>
-      <c r="E133" s="69"/>
-      <c r="F133" s="69"/>
-      <c r="G133" s="69"/>
-      <c r="H133" s="69"/>
+    <row r="132" spans="3:8" x14ac:dyDescent="0.2">
+      <c r="C132" s="66"/>
+      <c r="D132" s="66"/>
+      <c r="E132" s="66"/>
+      <c r="F132" s="66"/>
+      <c r="G132" s="66"/>
+      <c r="H132" s="67"/>
     </row>
     <row r="134" spans="3:8" x14ac:dyDescent="0.2">
       <c r="C134" s="69"/>
@@ -26356,6 +26395,14 @@
       <c r="F136" s="69"/>
       <c r="G136" s="69"/>
       <c r="H136" s="69"/>
+    </row>
+    <row r="137" spans="3:8" x14ac:dyDescent="0.2">
+      <c r="C137" s="69"/>
+      <c r="D137" s="69"/>
+      <c r="E137" s="69"/>
+      <c r="F137" s="69"/>
+      <c r="G137" s="69"/>
+      <c r="H137" s="69"/>
     </row>
   </sheetData>
   <mergeCells count="8">
@@ -26379,7 +26426,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="B1:I134"/>
+  <dimension ref="B1:I135"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="1.7109375" style="13" customWidth="1"/>
@@ -29136,22 +29183,22 @@
         <v>53</v>
       </c>
       <c r="C119" s="51">
-        <v>17.7329054073622</v>
+        <v>8.5143876907174096</v>
       </c>
       <c r="D119" s="51">
-        <v>1.7391900011492401</v>
+        <v>-2.6864561891104399</v>
       </c>
       <c r="E119" s="51">
-        <v>-10.392174519202801</v>
+        <v>-9.8337381063185596</v>
       </c>
       <c r="F119" s="51">
-        <v>3.0741749446289601</v>
+        <v>2.5808355999792099</v>
       </c>
       <c r="G119" s="51">
-        <v>7.2453995663194197</v>
+        <v>4.2411815470479599</v>
       </c>
       <c r="H119" s="51">
-        <v>2.39161402946739</v>
+        <v>-0.59503429813638298</v>
       </c>
       <c r="I119" s="61"/>
     </row>
@@ -29252,44 +29299,60 @@
       <c r="I123" s="61"/>
     </row>
     <row r="124" spans="2:9" s="1" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B124" s="48"/>
-      <c r="C124" s="49"/>
-      <c r="D124" s="49"/>
-      <c r="E124" s="49"/>
-      <c r="F124" s="49"/>
-      <c r="G124" s="49"/>
-      <c r="H124" s="49"/>
+      <c r="B124" s="48" t="s">
+        <v>11</v>
+      </c>
+      <c r="C124" s="49">
+        <v>1.9735542503433099</v>
+      </c>
+      <c r="D124" s="49">
+        <v>-52.529512336008899</v>
+      </c>
+      <c r="E124" s="49">
+        <v>7.2907934725372696</v>
+      </c>
+      <c r="F124" s="49">
+        <v>11.698688668407099</v>
+      </c>
+      <c r="G124" s="49">
+        <v>-18.463648810412099</v>
+      </c>
+      <c r="H124" s="49">
+        <v>-29.296982759909199</v>
+      </c>
       <c r="I124" s="61"/>
     </row>
-    <row r="125" spans="2:9" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="B125" s="63" t="s">
+    <row r="125" spans="2:9" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B125" s="48"/>
+      <c r="C125" s="49"/>
+      <c r="D125" s="49"/>
+      <c r="E125" s="49"/>
+      <c r="F125" s="49"/>
+      <c r="G125" s="49"/>
+      <c r="H125" s="49"/>
+      <c r="I125" s="61"/>
+    </row>
+    <row r="126" spans="2:9" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="B126" s="63" t="s">
         <v>52</v>
       </c>
-      <c r="C125" s="45"/>
-      <c r="D125" s="45"/>
-      <c r="E125" s="45"/>
-      <c r="F125" s="45"/>
-      <c r="G125" s="45"/>
-      <c r="H125" s="45"/>
-    </row>
-    <row r="126" spans="2:9" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="B126" s="64" t="s">
+      <c r="C126" s="45"/>
+      <c r="D126" s="45"/>
+      <c r="E126" s="45"/>
+      <c r="F126" s="45"/>
+      <c r="G126" s="45"/>
+      <c r="H126" s="45"/>
+    </row>
+    <row r="127" spans="2:9" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="B127" s="64" t="s">
         <v>21</v>
       </c>
-      <c r="C126" s="34"/>
-      <c r="D126" s="34"/>
-      <c r="E126" s="34"/>
-      <c r="F126" s="34"/>
-      <c r="G126" s="34"/>
-      <c r="H126" s="34"/>
-    </row>
-    <row r="128" spans="2:9" x14ac:dyDescent="0.2">
-      <c r="C128" s="66"/>
-      <c r="D128" s="66"/>
-      <c r="E128" s="66"/>
-      <c r="F128" s="66"/>
-      <c r="G128" s="66"/>
-      <c r="H128" s="67"/>
+      <c r="C127" s="34"/>
+      <c r="D127" s="34"/>
+      <c r="E127" s="34"/>
+      <c r="F127" s="34"/>
+      <c r="G127" s="34"/>
+      <c r="H127" s="34"/>
     </row>
     <row r="129" spans="3:8" x14ac:dyDescent="0.2">
       <c r="C129" s="66"/>
@@ -29313,7 +29376,7 @@
       <c r="E131" s="66"/>
       <c r="F131" s="66"/>
       <c r="G131" s="66"/>
-      <c r="H131" s="66"/>
+      <c r="H131" s="67"/>
     </row>
     <row r="132" spans="3:8" x14ac:dyDescent="0.2">
       <c r="C132" s="66"/>
@@ -29338,6 +29401,14 @@
       <c r="F134" s="66"/>
       <c r="G134" s="66"/>
       <c r="H134" s="66"/>
+    </row>
+    <row r="135" spans="3:8" x14ac:dyDescent="0.2">
+      <c r="C135" s="66"/>
+      <c r="D135" s="66"/>
+      <c r="E135" s="66"/>
+      <c r="F135" s="66"/>
+      <c r="G135" s="66"/>
+      <c r="H135" s="66"/>
     </row>
   </sheetData>
   <mergeCells count="8">

--- a/datos/indicadores_adelantados/transporte/indice_general_transporte_2017_2026.xlsx
+++ b/datos/indicadores_adelantados/transporte/indice_general_transporte_2017_2026.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\clopez\Documents\Transporte\TRANS AGQ\Cuadros de salida Transporte\Pagina web\Indicadores\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\clopez\Documents\TRANSPORTE\TRANS AGQ\Cuadros de salida Transporte\Pagina web\Indicadores\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0037C23E-747C-45FB-B2BA-55D8D7D7DCFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CAB1CB5-1A3A-402F-930A-3CF8B71B94AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="743" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,14 +23,14 @@
     <sheet name="Ponderadores" sheetId="14" state="hidden" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">Indice!$B$2:$H$141</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Indice!$B$2:$H$142</definedName>
   </definedNames>
   <calcPr calcId="181029" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="805" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="808" uniqueCount="59">
   <si>
     <t>PERIODO</t>
   </si>
@@ -20184,7 +20184,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B1:L149"/>
+  <dimension ref="B1:L150"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="1.7109375" style="1" customWidth="1"/>
@@ -23168,22 +23168,22 @@
         <v>53</v>
       </c>
       <c r="C133" s="51">
-        <v>85.647565273994701</v>
+        <v>87.092207734861205</v>
       </c>
       <c r="D133" s="51">
-        <v>88.998634781700005</v>
+        <v>79.801372783783194</v>
       </c>
       <c r="E133" s="51">
-        <v>117.410077812916</v>
+        <v>117.755787042004</v>
       </c>
       <c r="F133" s="51">
-        <v>89.5088107948106</v>
+        <v>89.691648433231606</v>
       </c>
       <c r="G133" s="51">
-        <v>85.327925407727605</v>
+        <v>82.978882508627294</v>
       </c>
       <c r="H133" s="51">
-        <v>90.207404815957005</v>
+        <v>85.567674730133405</v>
       </c>
     </row>
     <row r="134" spans="2:8" x14ac:dyDescent="0.2">
@@ -23223,13 +23223,13 @@
         <v>109.56670480906401</v>
       </c>
       <c r="F135" s="49">
-        <v>82.257435317945905</v>
+        <v>82.486337479037005</v>
       </c>
       <c r="G135" s="53">
         <v>82.505571671196805</v>
       </c>
       <c r="H135" s="49">
-        <v>86.980251269839798</v>
+        <v>86.991993950703801</v>
       </c>
     </row>
     <row r="136" spans="2:8" x14ac:dyDescent="0.2">
@@ -23246,13 +23246,13 @@
         <v>114.15337810267199</v>
       </c>
       <c r="F136" s="49">
-        <v>94.845983615156698</v>
+        <v>95.074804518909104</v>
       </c>
       <c r="G136" s="53">
         <v>91.742613290990505</v>
       </c>
       <c r="H136" s="49">
-        <v>101.33529060167101</v>
+        <v>101.347029114034</v>
       </c>
     </row>
     <row r="137" spans="2:8" x14ac:dyDescent="0.2">
@@ -23269,13 +23269,13 @@
         <v>112.51768668862201</v>
       </c>
       <c r="F137" s="49">
-        <v>83.571803919877397</v>
+        <v>83.804158724333206</v>
       </c>
       <c r="G137" s="53">
         <v>91.379535583741401</v>
       </c>
       <c r="H137" s="49">
-        <v>101.968461162241</v>
+        <v>101.980380963709</v>
       </c>
     </row>
     <row r="138" spans="2:8" x14ac:dyDescent="0.2">
@@ -23292,47 +23292,62 @@
         <v>120.721118845166</v>
       </c>
       <c r="F138" s="49">
-        <v>93.348609075035498</v>
+        <v>93.698837199810697</v>
       </c>
       <c r="G138" s="53">
         <v>74.507539048973797</v>
       </c>
       <c r="H138" s="49">
-        <v>72.094778674994501</v>
+        <v>72.112745377795505</v>
       </c>
     </row>
     <row r="139" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B139" s="48"/>
-      <c r="C139" s="53"/>
-      <c r="D139" s="53"/>
-      <c r="E139" s="53"/>
-      <c r="F139" s="49"/>
-      <c r="G139" s="53"/>
-      <c r="H139" s="49"/>
-    </row>
-    <row r="140" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B140" s="55" t="s">
+      <c r="B139" s="48" t="s">
+        <v>12</v>
+      </c>
+      <c r="C139" s="53">
+        <v>94.315420039193896</v>
+      </c>
+      <c r="D139" s="53">
+        <v>33.815062794199399</v>
+      </c>
+      <c r="E139" s="53">
+        <v>119.484333187445</v>
+      </c>
+      <c r="F139" s="49">
+        <v>89.565530631262305</v>
+      </c>
+      <c r="G139" s="53">
+        <v>71.233668013125495</v>
+      </c>
+      <c r="H139" s="49">
+        <v>62.3156566035194</v>
+      </c>
+    </row>
+    <row r="140" spans="2:8" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B140" s="48"/>
+      <c r="C140" s="53"/>
+      <c r="D140" s="53"/>
+      <c r="E140" s="53"/>
+      <c r="F140" s="49"/>
+      <c r="G140" s="53"/>
+      <c r="H140" s="49"/>
+    </row>
+    <row r="141" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B141" s="55" t="s">
         <v>52</v>
       </c>
-      <c r="C140" s="43"/>
-      <c r="D140" s="43"/>
-      <c r="E140" s="44"/>
-      <c r="F140" s="43"/>
-      <c r="G140" s="43"/>
-      <c r="H140" s="44"/>
-    </row>
-    <row r="141" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="B141" s="56" t="s">
+      <c r="C141" s="43"/>
+      <c r="D141" s="43"/>
+      <c r="E141" s="44"/>
+      <c r="F141" s="43"/>
+      <c r="G141" s="43"/>
+      <c r="H141" s="44"/>
+    </row>
+    <row r="142" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B142" s="56" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="142" spans="2:8" x14ac:dyDescent="0.2">
-      <c r="C142" s="65"/>
-      <c r="D142" s="65"/>
-      <c r="E142" s="65"/>
-      <c r="F142" s="65"/>
-      <c r="G142" s="65"/>
-      <c r="H142" s="65"/>
     </row>
     <row r="143" spans="2:8" x14ac:dyDescent="0.2">
       <c r="C143" s="65"/>
@@ -23359,12 +23374,12 @@
       <c r="H145" s="65"/>
     </row>
     <row r="146" spans="3:8" x14ac:dyDescent="0.2">
-      <c r="C146" s="68"/>
-      <c r="D146" s="68"/>
-      <c r="E146" s="68"/>
-      <c r="F146" s="68"/>
-      <c r="G146" s="68"/>
-      <c r="H146" s="68"/>
+      <c r="C146" s="65"/>
+      <c r="D146" s="65"/>
+      <c r="E146" s="65"/>
+      <c r="F146" s="65"/>
+      <c r="G146" s="65"/>
+      <c r="H146" s="65"/>
     </row>
     <row r="147" spans="3:8" x14ac:dyDescent="0.2">
       <c r="C147" s="68"/>
@@ -23389,6 +23404,14 @@
       <c r="F149" s="68"/>
       <c r="G149" s="68"/>
       <c r="H149" s="68"/>
+    </row>
+    <row r="150" spans="3:8" x14ac:dyDescent="0.2">
+      <c r="C150" s="68"/>
+      <c r="D150" s="68"/>
+      <c r="E150" s="68"/>
+      <c r="F150" s="68"/>
+      <c r="G150" s="68"/>
+      <c r="H150" s="68"/>
     </row>
   </sheetData>
   <mergeCells count="8">
@@ -23412,7 +23435,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="B1:I137"/>
+  <dimension ref="B1:I138"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="1.7109375" style="13" customWidth="1"/>
@@ -26169,22 +26192,22 @@
         <v>53</v>
       </c>
       <c r="C119" s="51">
-        <v>8.5143876907174096</v>
+        <v>5.9041371390831001</v>
       </c>
       <c r="D119" s="51">
-        <v>-2.6864561891104399</v>
+        <v>-6.9516321918771196</v>
       </c>
       <c r="E119" s="51">
-        <v>-9.8337381063185596</v>
+        <v>-9.4848465871623908</v>
       </c>
       <c r="F119" s="51">
-        <v>2.5808355999792099</v>
+        <v>2.1739821659236598</v>
       </c>
       <c r="G119" s="51">
-        <v>4.2411815470479599</v>
+        <v>1.6963779084239701</v>
       </c>
       <c r="H119" s="51">
-        <v>-0.59503429813638298</v>
+        <v>-3.2203843073128402</v>
       </c>
       <c r="I119" s="61"/>
     </row>
@@ -26226,13 +26249,13 @@
         <v>-7.7433764969202903</v>
       </c>
       <c r="F121" s="49">
-        <v>3.97498980040768</v>
+        <v>4.2643265609417798</v>
       </c>
       <c r="G121" s="49">
         <v>6.8624496891670903</v>
       </c>
       <c r="H121" s="49">
-        <v>-7.9001935646723203</v>
+        <v>-7.8877597234403396</v>
       </c>
       <c r="I121" s="61"/>
     </row>
@@ -26250,13 +26273,13 @@
         <v>-5.5355038084635702</v>
       </c>
       <c r="F122" s="49">
-        <v>9.5268428874073301</v>
+        <v>9.7910821331758804</v>
       </c>
       <c r="G122" s="49">
         <v>17.276122404854899</v>
       </c>
       <c r="H122" s="49">
-        <v>14.301356186007199</v>
+        <v>14.3145966659498</v>
       </c>
       <c r="I122" s="61"/>
     </row>
@@ -26274,13 +26297,13 @@
         <v>-9.0072444886629199</v>
       </c>
       <c r="F123" s="49">
-        <v>-4.4355154342652803</v>
+        <v>-4.1698173628741104</v>
       </c>
       <c r="G123" s="49">
         <v>7.5804950670356703</v>
       </c>
       <c r="H123" s="49">
-        <v>25.5381755991856</v>
+        <v>25.5528506282362</v>
       </c>
       <c r="I123" s="61"/>
     </row>
@@ -26298,55 +26321,71 @@
         <v>-7.6095878743040499</v>
       </c>
       <c r="F124" s="49">
-        <v>0.75113118193657202</v>
+        <v>1.1291323122422801</v>
       </c>
       <c r="G124" s="49">
         <v>-7.9459390819057596</v>
       </c>
       <c r="H124" s="49">
-        <v>-13.809465770313199</v>
+        <v>-13.787986271503099</v>
       </c>
       <c r="I124" s="61"/>
     </row>
     <row r="125" spans="2:9" s="1" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B125" s="48"/>
-      <c r="C125" s="49"/>
-      <c r="D125" s="49"/>
-      <c r="E125" s="49"/>
-      <c r="F125" s="49"/>
-      <c r="G125" s="49"/>
-      <c r="H125" s="49"/>
+      <c r="B125" s="48" t="s">
+        <v>12</v>
+      </c>
+      <c r="C125" s="49">
+        <v>-4.52366829704859</v>
+      </c>
+      <c r="D125" s="49">
+        <v>-40.988196091349799</v>
+      </c>
+      <c r="E125" s="49">
+        <v>-7.7306913261046297</v>
+      </c>
+      <c r="F125" s="49">
+        <v>-0.93981020480289601</v>
+      </c>
+      <c r="G125" s="49">
+        <v>-11.276321998842301</v>
+      </c>
+      <c r="H125" s="49">
+        <v>-18.810078778838399</v>
+      </c>
       <c r="I125" s="61"/>
     </row>
-    <row r="126" spans="2:9" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="B126" s="63" t="s">
+    <row r="126" spans="2:9" s="1" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B126" s="48"/>
+      <c r="C126" s="49"/>
+      <c r="D126" s="49"/>
+      <c r="E126" s="49"/>
+      <c r="F126" s="49"/>
+      <c r="G126" s="49"/>
+      <c r="H126" s="49"/>
+      <c r="I126" s="61"/>
+    </row>
+    <row r="127" spans="2:9" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="B127" s="63" t="s">
         <v>52</v>
       </c>
-      <c r="C126" s="45"/>
-      <c r="D126" s="45"/>
-      <c r="E126" s="45"/>
-      <c r="F126" s="45"/>
-      <c r="G126" s="45"/>
-      <c r="H126" s="45"/>
-    </row>
-    <row r="127" spans="2:9" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="B127" s="64" t="s">
+      <c r="C127" s="45"/>
+      <c r="D127" s="45"/>
+      <c r="E127" s="45"/>
+      <c r="F127" s="45"/>
+      <c r="G127" s="45"/>
+      <c r="H127" s="45"/>
+    </row>
+    <row r="128" spans="2:9" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="B128" s="64" t="s">
         <v>21</v>
       </c>
-      <c r="C127" s="34"/>
-      <c r="D127" s="34"/>
-      <c r="E127" s="34"/>
-      <c r="F127" s="34"/>
-      <c r="G127" s="34"/>
-      <c r="H127" s="34"/>
-    </row>
-    <row r="129" spans="3:8" x14ac:dyDescent="0.2">
-      <c r="C129" s="66"/>
-      <c r="D129" s="66"/>
-      <c r="E129" s="66"/>
-      <c r="F129" s="66"/>
-      <c r="G129" s="66"/>
-      <c r="H129" s="67"/>
+      <c r="C128" s="34"/>
+      <c r="D128" s="34"/>
+      <c r="E128" s="34"/>
+      <c r="F128" s="34"/>
+      <c r="G128" s="34"/>
+      <c r="H128" s="34"/>
     </row>
     <row r="130" spans="3:8" x14ac:dyDescent="0.2">
       <c r="C130" s="66"/>
@@ -26372,13 +26411,13 @@
       <c r="G132" s="66"/>
       <c r="H132" s="67"/>
     </row>
-    <row r="134" spans="3:8" x14ac:dyDescent="0.2">
-      <c r="C134" s="69"/>
-      <c r="D134" s="69"/>
-      <c r="E134" s="69"/>
-      <c r="F134" s="69"/>
-      <c r="G134" s="69"/>
-      <c r="H134" s="69"/>
+    <row r="133" spans="3:8" x14ac:dyDescent="0.2">
+      <c r="C133" s="66"/>
+      <c r="D133" s="66"/>
+      <c r="E133" s="66"/>
+      <c r="F133" s="66"/>
+      <c r="G133" s="66"/>
+      <c r="H133" s="67"/>
     </row>
     <row r="135" spans="3:8" x14ac:dyDescent="0.2">
       <c r="C135" s="69"/>
@@ -26403,6 +26442,14 @@
       <c r="F137" s="69"/>
       <c r="G137" s="69"/>
       <c r="H137" s="69"/>
+    </row>
+    <row r="138" spans="3:8" x14ac:dyDescent="0.2">
+      <c r="C138" s="69"/>
+      <c r="D138" s="69"/>
+      <c r="E138" s="69"/>
+      <c r="F138" s="69"/>
+      <c r="G138" s="69"/>
+      <c r="H138" s="69"/>
     </row>
   </sheetData>
   <mergeCells count="8">
@@ -26426,7 +26473,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="B1:I135"/>
+  <dimension ref="B1:I136"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="1.7109375" style="13" customWidth="1"/>
@@ -29183,22 +29230,22 @@
         <v>53</v>
       </c>
       <c r="C119" s="51">
-        <v>8.5143876907174096</v>
+        <v>5.9041371390831001</v>
       </c>
       <c r="D119" s="51">
-        <v>-2.6864561891104399</v>
+        <v>-6.9516321918771196</v>
       </c>
       <c r="E119" s="51">
-        <v>-9.8337381063185596</v>
+        <v>-9.4848465871623908</v>
       </c>
       <c r="F119" s="51">
-        <v>2.5808355999792099</v>
+        <v>2.1739821659236598</v>
       </c>
       <c r="G119" s="51">
-        <v>4.2411815470479599</v>
+        <v>1.6963779084239701</v>
       </c>
       <c r="H119" s="51">
-        <v>-0.59503429813638298</v>
+        <v>-3.2203843073128402</v>
       </c>
       <c r="I119" s="61"/>
     </row>
@@ -29240,13 +29287,13 @@
         <v>-15.777199672786599</v>
       </c>
       <c r="F121" s="49">
-        <v>-12.0431565298757</v>
+        <v>-11.798394321143499</v>
       </c>
       <c r="G121" s="49">
         <v>-4.6226518853395504</v>
       </c>
       <c r="H121" s="49">
-        <v>-1.8926509891502701</v>
+        <v>-1.879406105708</v>
       </c>
       <c r="I121" s="61"/>
     </row>
@@ -29264,13 +29311,13 @@
         <v>4.1861926044056199</v>
       </c>
       <c r="F122" s="49">
-        <v>15.3038424411761</v>
+        <v>15.2612752906763</v>
       </c>
       <c r="G122" s="49">
         <v>11.1956579812638</v>
       </c>
       <c r="H122" s="49">
-        <v>16.503791518487802</v>
+        <v>16.501558949740598</v>
       </c>
       <c r="I122" s="61"/>
     </row>
@@ -29288,13 +29335,13 @@
         <v>-1.4328891892965301</v>
       </c>
       <c r="F123" s="49">
-        <v>-11.8868287992299</v>
+        <v>-11.8545032531035</v>
       </c>
       <c r="G123" s="49">
         <v>-0.39575688355148497</v>
       </c>
       <c r="H123" s="49">
-        <v>0.62482730035171097</v>
+        <v>0.62493380931999798</v>
       </c>
       <c r="I123" s="61"/>
     </row>
@@ -29312,55 +29359,71 @@
         <v>7.2907934725372696</v>
       </c>
       <c r="F124" s="49">
-        <v>11.698688668407099</v>
+        <v>11.806906275409601</v>
       </c>
       <c r="G124" s="49">
         <v>-18.463648810412099</v>
       </c>
       <c r="H124" s="49">
-        <v>-29.296982759909199</v>
+        <v>-29.287628957321001</v>
       </c>
       <c r="I124" s="61"/>
     </row>
     <row r="125" spans="2:9" s="1" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B125" s="48"/>
-      <c r="C125" s="49"/>
-      <c r="D125" s="49"/>
-      <c r="E125" s="49"/>
-      <c r="F125" s="49"/>
-      <c r="G125" s="49"/>
-      <c r="H125" s="49"/>
+      <c r="B125" s="48" t="s">
+        <v>12</v>
+      </c>
+      <c r="C125" s="49">
+        <v>0.183517016913953</v>
+      </c>
+      <c r="D125" s="49">
+        <v>-37.289216469509697</v>
+      </c>
+      <c r="E125" s="49">
+        <v>-1.02449817360231</v>
+      </c>
+      <c r="F125" s="49">
+        <v>-4.4112677297523</v>
+      </c>
+      <c r="G125" s="49">
+        <v>-4.3940131128158599</v>
+      </c>
+      <c r="H125" s="49">
+        <v>-13.585793638766001</v>
+      </c>
       <c r="I125" s="61"/>
     </row>
-    <row r="126" spans="2:9" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="B126" s="63" t="s">
+    <row r="126" spans="2:9" s="1" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B126" s="48"/>
+      <c r="C126" s="49"/>
+      <c r="D126" s="49"/>
+      <c r="E126" s="49"/>
+      <c r="F126" s="49"/>
+      <c r="G126" s="49"/>
+      <c r="H126" s="49"/>
+      <c r="I126" s="61"/>
+    </row>
+    <row r="127" spans="2:9" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="B127" s="63" t="s">
         <v>52</v>
       </c>
-      <c r="C126" s="45"/>
-      <c r="D126" s="45"/>
-      <c r="E126" s="45"/>
-      <c r="F126" s="45"/>
-      <c r="G126" s="45"/>
-      <c r="H126" s="45"/>
-    </row>
-    <row r="127" spans="2:9" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="B127" s="64" t="s">
+      <c r="C127" s="45"/>
+      <c r="D127" s="45"/>
+      <c r="E127" s="45"/>
+      <c r="F127" s="45"/>
+      <c r="G127" s="45"/>
+      <c r="H127" s="45"/>
+    </row>
+    <row r="128" spans="2:9" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="B128" s="64" t="s">
         <v>21</v>
       </c>
-      <c r="C127" s="34"/>
-      <c r="D127" s="34"/>
-      <c r="E127" s="34"/>
-      <c r="F127" s="34"/>
-      <c r="G127" s="34"/>
-      <c r="H127" s="34"/>
-    </row>
-    <row r="129" spans="3:8" x14ac:dyDescent="0.2">
-      <c r="C129" s="66"/>
-      <c r="D129" s="66"/>
-      <c r="E129" s="66"/>
-      <c r="F129" s="66"/>
-      <c r="G129" s="66"/>
-      <c r="H129" s="67"/>
+      <c r="C128" s="34"/>
+      <c r="D128" s="34"/>
+      <c r="E128" s="34"/>
+      <c r="F128" s="34"/>
+      <c r="G128" s="34"/>
+      <c r="H128" s="34"/>
     </row>
     <row r="130" spans="3:8" x14ac:dyDescent="0.2">
       <c r="C130" s="66"/>
@@ -29384,7 +29447,7 @@
       <c r="E132" s="66"/>
       <c r="F132" s="66"/>
       <c r="G132" s="66"/>
-      <c r="H132" s="66"/>
+      <c r="H132" s="67"/>
     </row>
     <row r="133" spans="3:8" x14ac:dyDescent="0.2">
       <c r="C133" s="66"/>
@@ -29409,6 +29472,14 @@
       <c r="F135" s="66"/>
       <c r="G135" s="66"/>
       <c r="H135" s="66"/>
+    </row>
+    <row r="136" spans="3:8" x14ac:dyDescent="0.2">
+      <c r="C136" s="66"/>
+      <c r="D136" s="66"/>
+      <c r="E136" s="66"/>
+      <c r="F136" s="66"/>
+      <c r="G136" s="66"/>
+      <c r="H136" s="66"/>
     </row>
   </sheetData>
   <mergeCells count="8">
